--- a/Designer-Profile-Update.xlsx
+++ b/Designer-Profile-Update.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -54,11 +54,11 @@
   </si>
   <si>
     <t xml:space="preserve">1-5 
-(Empfohlen 3-5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Stunden
-(Erste Runde 3h)</t>
+(Recommended 3-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Hours
+(First Round 3h)</t>
   </si>
   <si>
     <t xml:space="preserve">Kenner-, bzw. Expertenspiel</t>
@@ -67,7 +67,9 @@
     <t xml:space="preserve">Kennerspiel</t>
   </si>
   <si>
-    <t xml:space="preserve">Wheel of Elements ist ein sehr schnelles kooperatives Strategiespiel.  Im Spiel geht es darum drei Kämpfe mit wachsenden Gegnergruppen zu bestreiten. Das Kampfsystem ist ähnlich zu Slay the Spire. Im titelgebenden „Wheel of Elements“ sammelt man gemeinsam Ressourcen um die stärksten Karten auszuspielen. Im Verlauf des Spiels sammelt man mehrere Klassen, welche einem Karten, Würfel und passive Effekte geben. Durch die hohe Eigenbestimmung passt sich das Spiel gut an verschiedene Gruppen an.</t>
+    <t xml:space="preserve">Wheel of Elements is a co-operative strategic card-battler, with a clear emphasis on (felt) speed and fluidity.
+Play through handcrafted stories, and forge your own martial path by combining classes inspired by the five Chinese elements. Coordinate powerful combos with your party, and manipulate the wheel of elements to empower your strongest cards.
+These meaningful choices let the game adapt to diverse player groups and result in high replayability.  </t>
   </si>
   <si>
     <t xml:space="preserve">Category</t>
@@ -110,10 +112,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="@"/>
     <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -251,7 +252,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -286,10 +287,6 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -400,37 +397,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -570,7 +567,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16.71"/>
@@ -584,7 +581,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="1" width="11.43"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -653,29 +650,29 @@
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F3" s="1" t="str">
         <f aca="false">"Zeichen/characters: " &amp; LEN(F2)</f>
-        <v>Zeichen/characters: 494</v>
-      </c>
-      <c r="L3" s="9" t="str">
+        <v>Zeichen/characters: 458</v>
+      </c>
+      <c r="L3" s="1" t="str">
         <f aca="false">"Zeichen/characters: " &amp; LEN(L2)</f>
         <v>Zeichen/characters: 0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F4" s="10" t="str">
+      <c r="F4" s="9" t="str">
         <f aca="false">IF(LEN(F2)&gt;500,"zu lang/too long - max 500","")</f>
         <v/>
       </c>
-      <c r="G4" s="10" t="str">
+      <c r="G4" s="9" t="str">
         <f aca="false">IF(LEN(G2)&gt;500,"zu lang/too long - max 500","")</f>
         <v/>
       </c>
-      <c r="L4" s="10" t="str">
+      <c r="L4" s="9" t="str">
         <f aca="false">IF(LEN(L2)&gt;500,"zu lang/too long - max 500","")</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="11"/>
+      <c r="C8" s="10"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="3yv05exFg9edege3n6RnwFPpRIEwMo/H99PsquMhbOpjVXIN5AoprJdImrHudTDi8FsAa5NDgQZ/oHKuwKAPxA==" saltValue="ii4eUc0x8rDw1mflY6APWg==" spinCount="100000" sheet="true" objects="true" scenarios="true"/>
@@ -715,70 +712,70 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="32.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="32.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>24</v>
       </c>
     </row>
